--- a/artfynd/A 51947-2025 artfynd.xlsx
+++ b/artfynd/A 51947-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132821169</v>
+        <v>132821166</v>
       </c>
       <c r="B2" t="n">
-        <v>79334</v>
+        <v>78393</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571737</v>
+        <v>571739</v>
       </c>
       <c r="R2" t="n">
-        <v>7204159</v>
+        <v>7204166</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132821170</v>
+        <v>132821174</v>
       </c>
       <c r="B3" t="n">
-        <v>83321</v>
+        <v>91970</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571747</v>
+        <v>571815</v>
       </c>
       <c r="R3" t="n">
-        <v>7204120</v>
+        <v>7203938</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132821181</v>
+        <v>132821172</v>
       </c>
       <c r="B4" t="n">
-        <v>79334</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571665</v>
+        <v>571749</v>
       </c>
       <c r="R4" t="n">
-        <v>7203916</v>
+        <v>7204065</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132821175</v>
+        <v>132821176</v>
       </c>
       <c r="B5" t="n">
-        <v>79334</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571814</v>
+        <v>571831</v>
       </c>
       <c r="R5" t="n">
-        <v>7203939</v>
+        <v>7203923</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132821183</v>
+        <v>132821180</v>
       </c>
       <c r="B6" t="n">
-        <v>79334</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571649</v>
+        <v>571664</v>
       </c>
       <c r="R6" t="n">
-        <v>7203856</v>
+        <v>7203917</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132821167</v>
+        <v>132821185</v>
       </c>
       <c r="B7" t="n">
-        <v>79334</v>
+        <v>91974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571737</v>
+        <v>571660</v>
       </c>
       <c r="R7" t="n">
-        <v>7204166</v>
+        <v>7203844</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132821178</v>
+        <v>132821170</v>
       </c>
       <c r="B8" t="n">
-        <v>79334</v>
+        <v>83363</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571804</v>
+        <v>571747</v>
       </c>
       <c r="R8" t="n">
-        <v>7203919</v>
+        <v>7204120</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,50 +1424,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132821179</v>
+        <v>132821162</v>
       </c>
       <c r="B9" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vinbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571697</v>
+        <v>572094</v>
       </c>
       <c r="R9" t="n">
-        <v>7203914</v>
+        <v>7204371</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1499,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,32 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132821172</v>
+        <v>132821163</v>
       </c>
       <c r="B10" t="n">
-        <v>91920</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571749</v>
+        <v>571998</v>
       </c>
       <c r="R10" t="n">
-        <v>7204065</v>
+        <v>7204329</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1606,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1643,14 +1638,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132821171</v>
+        <v>132821164</v>
       </c>
       <c r="B11" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1678,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571746</v>
+        <v>571973</v>
       </c>
       <c r="R11" t="n">
-        <v>7204117</v>
+        <v>7204310</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1713,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1723,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,14 +1745,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132821163</v>
+        <v>132821167</v>
       </c>
       <c r="B12" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1785,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571998</v>
+        <v>571737</v>
       </c>
       <c r="R12" t="n">
-        <v>7204329</v>
+        <v>7204166</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1820,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1830,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,14 +1852,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132821164</v>
+        <v>132821169</v>
       </c>
       <c r="B13" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1892,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>571973</v>
+        <v>571737</v>
       </c>
       <c r="R13" t="n">
-        <v>7204310</v>
+        <v>7204159</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1927,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1937,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,32 +1959,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132821174</v>
+        <v>132821171</v>
       </c>
       <c r="B14" t="n">
-        <v>91916</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1999,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>571815</v>
+        <v>571746</v>
       </c>
       <c r="R14" t="n">
-        <v>7203938</v>
+        <v>7204117</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2034,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2044,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,14 +2066,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132821189</v>
+        <v>132821175</v>
       </c>
       <c r="B15" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2106,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571656</v>
+        <v>571814</v>
       </c>
       <c r="R15" t="n">
-        <v>7203843</v>
+        <v>7203939</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2141,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2151,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2178,32 +2173,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132821176</v>
+        <v>132821177</v>
       </c>
       <c r="B16" t="n">
-        <v>91920</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2213,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571831</v>
+        <v>571836</v>
       </c>
       <c r="R16" t="n">
-        <v>7203923</v>
+        <v>7203928</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2285,32 +2280,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132821188</v>
+        <v>132821178</v>
       </c>
       <c r="B17" t="n">
-        <v>78346</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571657</v>
+        <v>571804</v>
       </c>
       <c r="R17" t="n">
-        <v>7203844</v>
+        <v>7203919</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2355,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2365,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2392,32 +2387,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132821166</v>
+        <v>132821181</v>
       </c>
       <c r="B18" t="n">
-        <v>78357</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2427,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571739</v>
+        <v>571665</v>
       </c>
       <c r="R18" t="n">
-        <v>7204166</v>
+        <v>7203916</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2462,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2472,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2499,32 +2494,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132821180</v>
+        <v>132821183</v>
       </c>
       <c r="B19" t="n">
-        <v>91920</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2534,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571664</v>
+        <v>571649</v>
       </c>
       <c r="R19" t="n">
-        <v>7203917</v>
+        <v>7203856</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2569,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2579,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2606,32 +2601,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132821187</v>
+        <v>132821189</v>
       </c>
       <c r="B20" t="n">
-        <v>83316</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2641,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571658</v>
+        <v>571656</v>
       </c>
       <c r="R20" t="n">
-        <v>7203844</v>
+        <v>7203843</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2676,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2686,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2713,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132821184</v>
+        <v>132821187</v>
       </c>
       <c r="B21" t="n">
-        <v>92340</v>
+        <v>83358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6040186</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>571660</v>
+        <v>571658</v>
       </c>
       <c r="R21" t="n">
-        <v>7203843</v>
+        <v>7203844</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2820,45 +2815,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132821185</v>
+        <v>132821182</v>
       </c>
       <c r="B22" t="n">
-        <v>91920</v>
+        <v>57972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Vinbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>571660</v>
+        <v>571649</v>
       </c>
       <c r="R22" t="n">
-        <v>7203844</v>
+        <v>7203858</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2927,10 +2927,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132821177</v>
+        <v>132821179</v>
       </c>
       <c r="B23" t="n">
-        <v>79334</v>
+        <v>57975</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,34 +2938,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Vinbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571836</v>
+        <v>571697</v>
       </c>
       <c r="R23" t="n">
-        <v>7203928</v>
+        <v>7203914</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2997,7 +3002,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3007,7 +3012,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3034,10 +3039,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132821162</v>
+        <v>132821188</v>
       </c>
       <c r="B24" t="n">
-        <v>79334</v>
+        <v>78382</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3045,21 +3050,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3069,10 +3074,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572094</v>
+        <v>571657</v>
       </c>
       <c r="R24" t="n">
-        <v>7204371</v>
+        <v>7203844</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3104,7 +3109,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3114,7 +3119,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3141,10 +3146,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132821182</v>
+        <v>132821184</v>
       </c>
       <c r="B25" t="n">
-        <v>57955</v>
+        <v>92366</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3152,39 +3157,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6040186</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Vinbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571649</v>
+        <v>571660</v>
       </c>
       <c r="R25" t="n">
-        <v>7203858</v>
+        <v>7203843</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
